--- a/data/trans_orig/IP09-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP09-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>758</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5879</t>
+          <t>5700</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3289</t>
+          <t>3567</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11003</t>
+          <t>11006</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,31%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9046</t>
+          <t>9007</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10300</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16231</t>
+          <t>15649</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16300</t>
+          <t>16297</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24014</t>
+          <t>23736</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>86,94%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1767</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7173</t>
+          <t>7360</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5375</t>
+          <t>5414</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13988</t>
+          <t>13536</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9218</t>
+          <t>9166</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18425</t>
+          <t>18984</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>43,09%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8523</t>
+          <t>8336</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13929</t>
+          <t>13843</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14371</t>
+          <t>14823</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22984</t>
+          <t>22945</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>25630</t>
+          <t>25071</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>34837</t>
+          <t>34889</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>79,19%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>5055</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>665</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>5875</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3111</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9748</t>
+          <t>9591</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>41,28%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2814</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6606</t>
+          <t>6623</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9469</t>
+          <t>9491</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14717</t>
+          <t>14701</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13488</t>
+          <t>13645</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20125</t>
+          <t>20108</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,54%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>702</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6475</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4616</t>
+          <t>4560</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11414</t>
+          <t>11418</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6119</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15724</t>
+          <t>15986</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>35,42%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16438</t>
+          <t>16634</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22208</t>
+          <t>22211</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10801</t>
+          <t>10797</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17599</t>
+          <t>17655</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29403</t>
+          <t>29141</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39008</t>
+          <t>38756</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>85,88%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8551</t>
+          <t>8235</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18823</t>
+          <t>18927</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17885</t>
+          <t>18238</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31518</t>
+          <t>31815</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28746</t>
+          <t>28478</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45033</t>
+          <t>46224</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>33,08%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37420</t>
+          <t>37316</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47692</t>
+          <t>48008</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>51960</t>
+          <t>51663</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>65593</t>
+          <t>65240</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>94688</t>
+          <t>93497</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>110975</t>
+          <t>111243</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,62%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2873</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9419</t>
+          <t>9080</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>3451</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11104</t>
+          <t>10872</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7844</t>
+          <t>7489</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17314</t>
+          <t>16937</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>52,77%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4646</t>
+          <t>4985</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11324</t>
+          <t>11192</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6923</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14408</t>
+          <t>14576</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14778</t>
+          <t>15155</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24248</t>
+          <t>24603</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>76,66%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6420</t>
+          <t>6048</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14268</t>
+          <t>14303</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4797</t>
+          <t>5022</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13549</t>
+          <t>13413</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13583</t>
+          <t>13574</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25147</t>
+          <t>25220</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,58%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13538</t>
+          <t>13503</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21386</t>
+          <t>21758</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17873</t>
+          <t>18009</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26625</t>
+          <t>26400</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>34081</t>
+          <t>34008</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>45645</t>
+          <t>45654</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,08%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11299</t>
+          <t>11103</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6326</t>
+          <t>6051</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14050</t>
+          <t>14267</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12683</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23123</t>
+          <t>23588</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>52,23%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8571</t>
+          <t>8767</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15436</t>
+          <t>15474</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11243</t>
+          <t>11026</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18967</t>
+          <t>19242</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>21576</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32481</t>
+          <t>32664</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>72,32%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2169</t>
+          <t>2191</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9005</t>
+          <t>8989</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4745</t>
+          <t>4786</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12531</t>
+          <t>12842</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8267</t>
+          <t>9181</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18785</t>
+          <t>19464</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>39,88%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12123</t>
+          <t>12139</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18959</t>
+          <t>18937</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15146</t>
+          <t>14835</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22932</t>
+          <t>22891</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30020</t>
+          <t>29341</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>40538</t>
+          <t>39624</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>81,19%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22240</t>
+          <t>22023</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35877</t>
+          <t>35934</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26651</t>
+          <t>26828</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42342</t>
+          <t>42523</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52464</t>
+          <t>53194</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74221</t>
+          <t>74540</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>40,23%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46992</t>
+          <t>46935</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>60629</t>
+          <t>60846</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>60077</t>
+          <t>59896</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>75768</t>
+          <t>75591</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>111068</t>
+          <t>110749</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>132825</t>
+          <t>132095</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,29%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>5846</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2168</t>
+          <t>2159</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7154</t>
+          <t>7099</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>4262</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10976</t>
+          <t>11249</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>62,92%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7028</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2555</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7541</t>
+          <t>7550</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6902</t>
+          <t>6629</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13683</t>
+          <t>13616</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,16%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4460</t>
+          <t>4695</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11549</t>
+          <t>11360</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4720</t>
+          <t>4511</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11907</t>
+          <t>11788</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10540</t>
+          <t>11129</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20742</t>
+          <t>21654</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>54,63%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8047</t>
+          <t>8236</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15136</t>
+          <t>14901</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8134</t>
+          <t>8253</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15321</t>
+          <t>15530</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18894</t>
+          <t>17982</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29096</t>
+          <t>28507</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>71,92%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5428</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6875</t>
+          <t>6645</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4370</t>
+          <t>4040</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10810</t>
+          <t>10512</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>58,15%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>3580</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7874</t>
+          <t>7917</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2193</t>
+          <t>2423</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>7071</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7267</t>
+          <t>7565</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13707</t>
+          <t>14037</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>77,65%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2375</t>
+          <t>2468</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8013</t>
+          <t>7983</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4242</t>
+          <t>3854</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9886</t>
+          <t>9838</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8218</t>
+          <t>8044</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16182</t>
+          <t>16178</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,41%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2367</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7975</t>
+          <t>7882</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2743</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>8775</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6796</t>
+          <t>6800</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14760</t>
+          <t>14934</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,99%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13716</t>
+          <t>13995</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24245</t>
+          <t>24775</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17685</t>
+          <t>18024</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29248</t>
+          <t>29737</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34396</t>
+          <t>35470</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50248</t>
+          <t>51558</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>52,31%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22878</t>
+          <t>22348</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33407</t>
+          <t>33128</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22199</t>
+          <t>21710</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33762</t>
+          <t>33423</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>48322</t>
+          <t>47012</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>64174</t>
+          <t>63100</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>64,01%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>1803</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7024</t>
+          <t>6901</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>898</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10783</t>
+          <t>10452</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2701</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15413</t>
+          <t>14591</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>40,6%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4982</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10511</t>
+          <t>10203</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13148</t>
+          <t>13479</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22944</t>
+          <t>23033</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20524</t>
+          <t>21346</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33048</t>
+          <t>33236</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5087</t>
+          <t>4888</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18006</t>
+          <t>17313</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7090</t>
+          <t>7150</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15765</t>
+          <t>16034</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14979</t>
+          <t>15410</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31413</t>
+          <t>31098</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>65,75%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3354</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16273</t>
+          <t>16472</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10170</t>
+          <t>9901</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18845</t>
+          <t>18785</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15882</t>
+          <t>16197</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32316</t>
+          <t>31885</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>67,42%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1801</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2808</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10927</t>
+          <t>11587</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5945</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16186</t>
+          <t>16862</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>48,59%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5755</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11942</t>
+          <t>11856</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10033</t>
+          <t>9373</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18416</t>
+          <t>18152</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18517</t>
+          <t>17841</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28758</t>
+          <t>28695</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,69%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2187</t>
+          <t>2321</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8320</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>3694</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12040</t>
+          <t>11652</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7894</t>
+          <t>7387</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17737</t>
+          <t>17501</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>39,89%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7353</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13486</t>
+          <t>13352</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16164</t>
+          <t>16552</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24345</t>
+          <t>24510</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26140</t>
+          <t>26376</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>35983</t>
+          <t>36490</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>83,16%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17385</t>
+          <t>17052</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37000</t>
+          <t>35165</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18953</t>
+          <t>19946</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38918</t>
+          <t>39888</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41883</t>
+          <t>39976</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70448</t>
+          <t>69126</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>42,72%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25782</t>
+          <t>27617</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45397</t>
+          <t>45730</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>60111</t>
+          <t>59141</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>80076</t>
+          <t>79083</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>91363</t>
+          <t>92685</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>119928</t>
+          <t>121835</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>75,29%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP09-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP09-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3999</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1489</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8012</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>22,81%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>8,49%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>45,69%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2860</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>758</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5700</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>753</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5836</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>29,28%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,76%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>58,38%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3999</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1888</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7217</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>22,81%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3567</t>
+          <t>3419</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11006</t>
+          <t>11029</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,39%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>13538</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9525</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>16048</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>77,19%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>54,31%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>91,51%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>6905</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4065</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9007</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3929</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>9012</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>70,72%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>41,62%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>92,24%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>13538</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>10320</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>15649</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>77,19%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16297</t>
+          <t>16274</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23736</t>
+          <t>23884</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>87,48%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>17537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>9765</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>9765</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>9765</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>17537</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>17537</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>17537</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9403</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6027</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>14095</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>33,16%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>21,25%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>49,7%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>4337</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1853</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7360</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1900</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7372</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>27,63%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>11,81%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>46,89%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>9403</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>5414</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>13536</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>33,16%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9166</t>
+          <t>8691</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18984</t>
+          <t>18753</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>42,57%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18956</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>14264</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>22332</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>66,84%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>50,3%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>78,75%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>11359</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>8336</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>13843</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>8324</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>13796</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>72,37%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>53,11%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>88,19%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>18956</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>14823</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>22945</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>66,84%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>25071</t>
+          <t>25302</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>34889</t>
+          <t>35364</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>80,27%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>28359</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>28359</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>28359</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>15696</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>15696</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>15696</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>28359</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>28359</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>28359</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2653</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5444</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>17,27%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>35,43%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3130</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1246</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5055</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1240</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5554</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>39,77%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15,83%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>64,24%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2653</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5875</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>17,27%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>2708</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9591</t>
+          <t>9575</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,21%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>12713</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>9922</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>14659</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>82,73%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>64,57%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,4%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>4739</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2814</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6623</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2315</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>6629</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>60,23%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>35,76%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>84,17%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>12713</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>9491</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>14701</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>82,73%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13645</t>
+          <t>13661</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20108</t>
+          <t>20528</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>88,35%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15366</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>15366</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>15366</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>7869</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>7869</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>7869</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>15366</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>15366</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>15366</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7986</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4608</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11867</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>35,95%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>20,74%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>53,42%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2474</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>702</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6279</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5992</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>10,8%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>27,4%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>7986</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>4560</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>11418</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>35,95%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>6623</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15986</t>
+          <t>15952</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,35%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>14229</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>10348</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>17607</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>64,05%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>46,58%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>79,26%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>20439</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>16634</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>22211</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>16921</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>22208</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>89,2%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>72,6%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,94%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>14229</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>10797</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>17655</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>64,05%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29141</t>
+          <t>29175</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>38756</t>
+          <t>38504</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,32%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>22215</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>22215</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>22215</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>22913</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>22913</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>22913</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>22215</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>22215</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>22215</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>24042</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>18092</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>30739</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>28,8%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>21,67%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>36,82%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>12800</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>8235</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>18927</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>8067</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>18237</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>22,76%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>14,64%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>33,65%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>24042</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>18238</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>31815</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>28,8%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28478</t>
+          <t>29266</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46224</t>
+          <t>46196</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,06%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>59436</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>52739</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>65386</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>71,2%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>63,18%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>78,33%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>43443</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>37316</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>48008</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>38006</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>48176</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>77,24%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>66,35%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>85,36%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>59436</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>51663</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>65240</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>71,2%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>93497</t>
+          <t>93525</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>111243</t>
+          <t>110455</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>79,05%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>83478</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>83478</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>83478</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>56243</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>56243</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>56243</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>83478</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>83478</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>83478</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6901</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3587</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10761</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>38,28%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>19,9%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>59,69%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>5621</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2873</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9080</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2466</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>9184</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>39,96%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>20,43%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>64,56%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6901</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3451</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>10872</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>38,28%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7489</t>
+          <t>7919</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16937</t>
+          <t>17244</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>53,73%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11126</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7266</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>14440</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>61,72%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>40,31%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>80,1%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>8444</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4985</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>11192</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>4881</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>11599</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>60,04%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>35,44%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>79,57%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>11126</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>7155</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>14576</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>61,72%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15155</t>
+          <t>14848</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24603</t>
+          <t>24173</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>75,32%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>18027</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>18027</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>18027</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>14065</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>14065</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>14065</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>18027</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>18027</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>18027</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8928</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4419</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13310</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>28,41%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>14,06%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>42,36%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>10088</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6048</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>14303</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>6836</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>14490</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>36,28%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>21,75%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>51,44%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>8928</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>5022</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>13413</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>28,41%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13574</t>
+          <t>13851</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25220</t>
+          <t>25546</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>43,13%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>22494</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>18112</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>27003</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>71,59%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>57,64%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>85,94%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>17718</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>13503</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>21758</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>13316</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>20970</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>63,72%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>48,56%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>78,25%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>22494</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>18009</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>26400</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>71,59%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>34008</t>
+          <t>33682</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>45654</t>
+          <t>45377</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>76,61%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>31422</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>31422</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>31422</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>27806</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>27806</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>27806</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>31422</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>31422</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>31422</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10112</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6204</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13977</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>39,98%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>24,53%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>55,26%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>7633</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4396</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11103</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4415</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>11356</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>38,41%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>22,13%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>55,88%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>10112</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>6051</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>14267</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>39,98%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>12882</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23588</t>
+          <t>23281</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>51,55%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>15181</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>11316</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>19089</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>60,02%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>44,74%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>75,47%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>12237</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>8767</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>15474</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>8514</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>15455</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>61,59%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>44,12%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>77,87%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>15181</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>11026</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>19242</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>60,02%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21576</t>
+          <t>21883</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32664</t>
+          <t>32282</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>71,48%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>25293</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>25293</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>25293</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>19870</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>19870</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>19870</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>25293</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>25293</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>25293</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8311</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4803</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12868</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>30,03%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>17,36%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>46,49%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>5056</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2191</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8989</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2129</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8897</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>23,93%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10,37%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>42,54%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>8311</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>4786</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>12842</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>30,03%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9181</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19464</t>
+          <t>19255</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,45%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>19366</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>14809</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>22874</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>69,97%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>53,51%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>82,64%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>16072</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>12139</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>18937</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>12231</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>18999</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>76,07%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>57,46%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>89,63%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>19366</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>14835</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>22891</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>69,97%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29341</t>
+          <t>29550</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39624</t>
+          <t>39879</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,71%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>27677</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>27677</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>27677</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>21128</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>21128</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>21128</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>27677</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>27677</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>27677</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>34252</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>26680</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>43680</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>33,44%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>26,05%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>42,65%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>28397</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>22023</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>35934</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>21589</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>35499</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>34,27%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>26,58%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>43,36%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>34252</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>26828</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>42523</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>33,44%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53194</t>
+          <t>53598</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74540</t>
+          <t>74753</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,34%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>68167</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>58739</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>75739</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>66,56%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>57,35%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>73,95%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>54472</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>46935</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>60846</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>47370</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>61280</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>65,73%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>56,64%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>73,42%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>68167</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>59896</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>75591</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>66,56%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>110749</t>
+          <t>110536</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>132095</t>
+          <t>131691</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,07%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>102419</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>102419</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>102419</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>82869</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>82869</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>82869</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>102419</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>102419</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>102419</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4386</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1534</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6872</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>45,18%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>15,8%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>70,78%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3254</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1109</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5846</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1174</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5958</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>39,83%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>13,58%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>71,57%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4386</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2159</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7099</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>45,18%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4501</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11249</t>
+          <t>11663</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>65,24%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5323</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2837</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8175</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>54,82%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>29,22%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>84,2%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>4915</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2323</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7060</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2211</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>6995</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>60,17%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>28,43%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>86,42%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>5323</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2610</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>7550</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>54,82%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6629</t>
+          <t>6215</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13616</t>
+          <t>13377</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>74,82%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9709</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9709</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9709</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>8169</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>8169</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>8169</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>9709</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>9709</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>9709</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7945</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4804</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11941</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>39,64%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>23,97%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>59,58%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>7779</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4695</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>11360</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4442</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>11184</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>39,69%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>23,96%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>57,97%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>7945</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>4511</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>11788</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>39,64%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11129</t>
+          <t>11174</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21654</t>
+          <t>21254</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>53,62%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12096</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8100</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>15237</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>60,36%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>40,42%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>76,03%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>11817</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>8236</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>14901</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>8412</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>15154</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>60,31%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>42,03%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>76,04%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>12096</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>8253</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>15530</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>60,36%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>17982</t>
+          <t>18382</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28507</t>
+          <t>28462</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>71,81%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>20041</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>20041</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>20041</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>19596</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>19596</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>19596</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>20041</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>20041</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>20041</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4323</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6547</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>47,67%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>24,19%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>72,2%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2886</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1091</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5428</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1123</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5354</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>32,04%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,11%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>60,26%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4323</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6645</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>47,67%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4040</t>
+          <t>4488</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10512</t>
+          <t>10504</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,11%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4745</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2521</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6874</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>52,33%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>27,8%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>75,81%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>6122</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>3580</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>7917</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>3654</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>7885</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>67,96%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>39,74%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>87,89%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>4745</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2423</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>7071</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>52,33%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7565</t>
+          <t>7573</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14037</t>
+          <t>13589</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>75,17%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9068</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9068</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9068</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>9008</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>9008</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>9008</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>9068</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>9068</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>9068</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7121</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4070</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9901</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>56,39%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>32,22%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>78,4%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>5159</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2468</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7983</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2354</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7731</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>49,84%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>23,85%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>77,13%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>7121</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3854</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9838</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>56,39%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8044</t>
+          <t>7600</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16178</t>
+          <t>15980</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>69,54%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5508</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2728</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8559</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>43,61%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>21,6%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>67,78%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>5191</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2367</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>7882</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2619</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>7996</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>50,16%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>22,87%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>76,15%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>5508</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>2791</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>8775</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>43,61%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6800</t>
+          <t>6998</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14934</t>
+          <t>15378</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>66,93%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>12629</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>12629</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>12629</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>10350</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>10350</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>10350</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>12629</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>12629</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>12629</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>23775</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>18195</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>29911</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>46,21%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>35,37%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>58,14%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>19077</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>13995</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>24775</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>13988</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>24681</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>40,48%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>29,7%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>52,57%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>23775</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>18024</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>29737</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>46,21%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35470</t>
+          <t>35337</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51558</t>
+          <t>51256</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,0%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>27672</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>21536</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>33252</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>53,79%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>41,86%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>64,63%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>28046</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>22348</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>33128</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>22442</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>33135</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>59,52%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>47,43%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>70,3%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>27672</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>21710</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>33423</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>53,79%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47012</t>
+          <t>47314</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>63100</t>
+          <t>63233</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>64,15%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>47123</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>47123</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>47123</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>51447</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>51447</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>51447</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4129</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>858</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9425</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>20,01%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,16%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>45,68%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4053</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1803</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6901</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>33,76%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>15,02%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>57,48%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4507</t>
+          <t>4370</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>1644</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10452</t>
+          <t>7381</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>8560</t>
+          <t>8499</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14591</t>
+          <t>13939</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>42,06%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16504</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11208</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>19775</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>79,99%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>54,32%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>95,84%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>7953</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5105</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10203</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>66,24%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>42,52%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>84,98%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19424</t>
+          <t>8141</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13479</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23033</t>
+          <t>10867</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>27377</t>
+          <t>24645</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21346</t>
+          <t>19205</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33236</t>
+          <t>30024</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>90,59%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20633</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20633</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>20633</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>12006</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>12006</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>12006</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23931</t>
+          <t>12511</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23931</t>
+          <t>12511</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23931</t>
+          <t>12511</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>35937</t>
+          <t>33144</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>35937</t>
+          <t>33144</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35937</t>
+          <t>33144</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10807</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6784</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>14616</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>46,37%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>29,11%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>62,71%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>10702</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4888</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>17313</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>50,1%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>22,88%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>81,06%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11305</t>
+          <t>5919</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7150</t>
+          <t>3024</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16034</t>
+          <t>9554</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>22007</t>
+          <t>16726</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15410</t>
+          <t>11723</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31098</t>
+          <t>21908</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>55,53%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12500</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8691</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>16523</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>53,63%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>37,29%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>70,89%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>10658</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>4047</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>16472</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>49,9%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>18,94%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>77,12%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>14630</t>
+          <t>10227</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9901</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18785</t>
+          <t>13122</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>25288</t>
+          <t>22728</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16197</t>
+          <t>17546</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31885</t>
+          <t>27731</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>70,29%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>23307</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>23307</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>23307</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>21360</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>21360</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>21360</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25935</t>
+          <t>16146</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25935</t>
+          <t>16146</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25935</t>
+          <t>16146</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>47295</t>
+          <t>39454</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>47295</t>
+          <t>39454</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>47295</t>
+          <t>39454</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6190</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2466</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10466</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>31,17%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>12,42%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>52,7%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4265</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1887</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7480</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>31,03%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,73%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>54,43%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6484</t>
+          <t>4126</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11587</t>
+          <t>7451</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>10749</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16862</t>
+          <t>16055</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>47,5%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>13668</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>9392</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>17392</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>68,83%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>47,3%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>87,58%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>9478</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>6263</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>11856</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>68,97%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>45,57%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>86,27%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14476</t>
+          <t>9818</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9373</t>
+          <t>6493</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18152</t>
+          <t>12196</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>23954</t>
+          <t>23487</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17841</t>
+          <t>17747</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28695</t>
+          <t>28100</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>83,13%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>19858</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>19858</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>19858</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>13743</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>13743</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>13743</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20960</t>
+          <t>13944</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20960</t>
+          <t>13944</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20960</t>
+          <t>13944</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>34703</t>
+          <t>33802</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>34703</t>
+          <t>33802</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>34703</t>
+          <t>33802</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6556</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3568</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10704</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>26,15%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>14,23%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>42,69%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>4882</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2321</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8172</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>31,15%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>14,81%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>52,14%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7304</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3694</t>
+          <t>2192</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11652</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>12186</t>
+          <t>11251</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7387</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17501</t>
+          <t>16360</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>40,16%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>18517</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>14369</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>21505</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>73,85%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>57,31%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>85,77%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>10791</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>13352</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>68,85%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>47,86%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>85,19%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>20900</t>
+          <t>10970</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16552</t>
+          <t>7554</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24510</t>
+          <t>13474</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>31691</t>
+          <t>29488</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26376</t>
+          <t>24379</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36490</t>
+          <t>33578</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>82,42%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>25073</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>25073</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>25073</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>15673</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>15673</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>15673</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28204</t>
+          <t>15666</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28204</t>
+          <t>15666</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28204</t>
+          <t>15666</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>43877</t>
+          <t>40739</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>43877</t>
+          <t>40739</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>43877</t>
+          <t>40739</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>27682</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>17739</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>36240</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>31,15%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>19,96%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>40,78%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>23901</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>17052</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>35165</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>38,07%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>27,16%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>56,01%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>29601</t>
+          <t>19110</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19946</t>
+          <t>13376</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39888</t>
+          <t>24933</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>53502</t>
+          <t>46792</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39976</t>
+          <t>36173</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69126</t>
+          <t>58177</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>39,54%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>61189</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>52631</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>71132</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>68,85%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>59,22%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>80,04%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>38881</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>27617</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>45730</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>61,93%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>43,99%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>72,84%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>69428</t>
+          <t>39158</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59141</t>
+          <t>33335</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>79083</t>
+          <t>44892</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>108309</t>
+          <t>100347</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>92685</t>
+          <t>88962</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>121835</t>
+          <t>110966</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,42%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>88871</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>88871</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>88871</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>62782</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>62782</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>62782</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>58268</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>58268</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>58268</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>161811</t>
+          <t>147139</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>161811</t>
+          <t>147139</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>161811</t>
+          <t>147139</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
